--- a/salidas/empresas/BNY.xlsx
+++ b/salidas/empresas/BNY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>21.10311126708984</v>
+        <v>21.10313034057617</v>
       </c>
       <c r="C2" t="n">
         <v>33.71846389770508</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>23.90935707092285</v>
+        <v>23.90934944152832</v>
       </c>
       <c r="C4" t="n">
         <v>38.20224761962891</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.4629020690918</v>
+        <v>23.46290969848633</v>
       </c>
       <c r="C5" t="n">
         <v>37.25885009765625</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.18129348754883</v>
+        <v>22.1812915802002</v>
       </c>
       <c r="C6" t="n">
         <v>35.22365951538086</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.49375534057617</v>
+        <v>21.49374961853027</v>
       </c>
       <c r="C7" t="n">
         <v>34.13186264038086</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>22.58399963378906</v>
+        <v>22.58400917053223</v>
       </c>
       <c r="C8" t="n">
         <v>35.62645721435547</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.6780834197998</v>
+        <v>22.67808723449707</v>
       </c>
       <c r="C9" t="n">
         <v>35.77485656738281</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>23.69271087646484</v>
+        <v>23.69271850585938</v>
       </c>
       <c r="C10" t="n">
         <v>37.37545013427734</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.24699401855469</v>
+        <v>23.24699974060059</v>
       </c>
       <c r="C11" t="n">
         <v>36.43205261230469</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.03835487365723</v>
+        <v>24.0383472442627</v>
       </c>
       <c r="C12" t="n">
         <v>37.67224884033203</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.62885856628418</v>
+        <v>26.62887763977051</v>
       </c>
       <c r="C13" t="n">
         <v>41.73203277587891</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.20766448974609</v>
+        <v>27.2076587677002</v>
       </c>
       <c r="C14" t="n">
         <v>42.41043090820312</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>27.62928581237793</v>
+        <v>27.62928199768066</v>
       </c>
       <c r="C15" t="n">
         <v>43.067626953125</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>27.57488059997559</v>
+        <v>27.57485961914062</v>
       </c>
       <c r="C16" t="n">
         <v>42.98282623291016</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.67397689819336</v>
+        <v>27.67398452758789</v>
       </c>
       <c r="C17" t="n">
         <v>42.90862655639648</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.72867202758789</v>
+        <v>27.72866058349609</v>
       </c>
       <c r="C18" t="n">
         <v>42.99342727661133</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.33027267456055</v>
+        <v>28.33028221130371</v>
       </c>
       <c r="C19" t="n">
         <v>43.92622375488281</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.5909538269043</v>
+        <v>27.59094619750977</v>
       </c>
       <c r="C20" t="n">
         <v>42.54999923706055</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>26.21627235412598</v>
+        <v>26.21626663208008</v>
       </c>
       <c r="C21" t="n">
         <v>40.43000030517578</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.62197685241699</v>
+        <v>28.6219654083252</v>
       </c>
       <c r="C22" t="n">
         <v>44.13999938964844</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.78506469726562</v>
+        <v>31.78507232666016</v>
       </c>
       <c r="C25" t="n">
         <v>48.7599983215332</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.48830986022949</v>
+        <v>30.48833274841309</v>
       </c>
       <c r="C26" t="n">
         <v>46.52000045776367</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.75156402587891</v>
+        <v>28.75156593322754</v>
       </c>
       <c r="C27" t="n">
         <v>43.86999893188477</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.34903526306152</v>
+        <v>27.34903717041016</v>
       </c>
       <c r="C28" t="n">
         <v>41.72999954223633</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>28.69124984741211</v>
+        <v>28.69125366210938</v>
       </c>
       <c r="C29" t="n">
         <v>43.52999877929688</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.35036468505859</v>
+        <v>29.35036849975586</v>
       </c>
       <c r="C30" t="n">
         <v>44.52999877929688</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.93429946899414</v>
+        <v>24.93429756164551</v>
       </c>
       <c r="C31" t="n">
         <v>37.83000183105469</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.55577850341797</v>
+        <v>23.5557746887207</v>
       </c>
       <c r="C32" t="n">
         <v>35.5</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.96522331237793</v>
+        <v>22.96522903442383</v>
       </c>
       <c r="C33" t="n">
         <v>34.61000061035156</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.61822700500488</v>
+        <v>21.61823081970215</v>
       </c>
       <c r="C34" t="n">
         <v>32.58000183105469</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>22.05781364440918</v>
+        <v>22.05780792236328</v>
       </c>
       <c r="C35" t="n">
         <v>32.9900016784668</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.19904327392578</v>
+        <v>20.19903945922852</v>
       </c>
       <c r="C36" t="n">
         <v>30.20999908447266</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.94203948974609</v>
+        <v>18.94203567504883</v>
       </c>
       <c r="C37" t="n">
         <v>28.32999992370605</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.43048667907715</v>
+        <v>17.43047523498535</v>
       </c>
       <c r="C38" t="n">
         <v>25.73999977111816</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.01297092437744</v>
+        <v>15.01296806335449</v>
       </c>
       <c r="C39" t="n">
         <v>22.17000007629395</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.13018989562988</v>
+        <v>19.13019180297852</v>
       </c>
       <c r="C40" t="n">
         <v>28.25</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.31670379638672</v>
+        <v>17.31671142578125</v>
       </c>
       <c r="C41" t="n">
         <v>25.47999954223633</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>18.87982368469238</v>
+        <v>18.87983703613281</v>
       </c>
       <c r="C42" t="n">
         <v>27.78000068664551</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.64266967773438</v>
+        <v>18.64267539978027</v>
       </c>
       <c r="C44" t="n">
         <v>27.34000015258789</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.19053840637207</v>
+        <v>20.19054412841797</v>
       </c>
       <c r="C45" t="n">
         <v>29.61000061035156</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>19.76777458190918</v>
+        <v>19.76777076721191</v>
       </c>
       <c r="C46" t="n">
         <v>28.98999977111816</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.22442817687988</v>
+        <v>18.22443389892578</v>
       </c>
       <c r="C48" t="n">
         <v>26.63999938964844</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.13428688049316</v>
+        <v>19.1342945098877</v>
       </c>
       <c r="C49" t="n">
         <v>27.96999931335449</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.96085166931152</v>
+        <v>19.96084213256836</v>
       </c>
       <c r="C50" t="n">
         <v>29.09000015258789</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.56972885131836</v>
+        <v>19.56972312927246</v>
       </c>
       <c r="C51" t="n">
         <v>28.52000045776367</v>
@@ -1476,11 +1488,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.1891040802002</v>
+        <v>21.18910026550293</v>
       </c>
       <c r="C52" t="n">
         <v>30.8799991607666</v>
@@ -1503,11 +1515,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.42310333251953</v>
+        <v>21.423095703125</v>
       </c>
       <c r="C53" t="n">
         <v>31.1299991607666</v>
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1584,11 +1596,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.31230735778809</v>
+        <v>17.31230926513672</v>
       </c>
       <c r="C56" t="n">
         <v>25.06999969482422</v>
@@ -1611,11 +1623,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.75294876098633</v>
+        <v>16.75295257568359</v>
       </c>
       <c r="C57" t="n">
         <v>24.26000022888184</v>
@@ -1638,11 +1650,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.0442943572998</v>
+        <v>18.0443000793457</v>
       </c>
       <c r="C58" t="n">
         <v>26.1299991607666</v>
@@ -1665,11 +1677,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.36785697937012</v>
+        <v>17.36784934997559</v>
       </c>
       <c r="C59" t="n">
         <v>25.05999946594238</v>
@@ -1692,11 +1704,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>18.70543479919434</v>
+        <v>18.70543098449707</v>
       </c>
       <c r="C60" t="n">
         <v>26.98999977111816</v>
@@ -1721,11 +1733,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.93012809753418</v>
+        <v>20.93012428283691</v>
       </c>
       <c r="C61" t="n">
         <v>30.20000076293945</v>
@@ -1750,11 +1762,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>21.70557022094727</v>
+        <v>21.70557594299316</v>
       </c>
       <c r="C62" t="n">
         <v>31.22999954223633</v>
@@ -1779,11 +1791,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.12175559997559</v>
+        <v>21.12176322937012</v>
       </c>
       <c r="C63" t="n">
         <v>30.38999938964844</v>
@@ -1808,7 +1820,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1837,11 +1849,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>20.21945953369141</v>
+        <v>20.21946334838867</v>
       </c>
       <c r="C65" t="n">
         <v>28.95999908447266</v>
@@ -1866,11 +1878,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>19.62600517272949</v>
+        <v>19.62600326538086</v>
       </c>
       <c r="C66" t="n">
         <v>28.11000061035156</v>
@@ -1895,7 +1907,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1953,11 +1965,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.50484085083008</v>
+        <v>14.50483512878418</v>
       </c>
       <c r="C69" t="n">
         <v>20.67000007629395</v>
@@ -1982,11 +1994,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>13.04523277282715</v>
+        <v>13.0452299118042</v>
       </c>
       <c r="C70" t="n">
         <v>18.59000015258789</v>
@@ -2011,11 +2023,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.02610206604004</v>
+        <v>15.02609157562256</v>
       </c>
       <c r="C71" t="n">
         <v>21.28000068664551</v>
@@ -2040,7 +2052,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2069,11 +2081,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.05871772766113</v>
+        <v>14.0587215423584</v>
       </c>
       <c r="C73" t="n">
         <v>19.90999984741211</v>
@@ -2098,11 +2110,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.30446434020996</v>
+        <v>14.30446624755859</v>
       </c>
       <c r="C74" t="n">
         <v>20.1299991607666</v>
@@ -2127,11 +2139,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.71146583557129</v>
+        <v>15.71147441864014</v>
       </c>
       <c r="C75" t="n">
         <v>22.11000061035156</v>
@@ -2156,11 +2168,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>17.14688110351562</v>
+        <v>17.14688873291016</v>
       </c>
       <c r="C76" t="n">
         <v>24.1299991607666</v>
@@ -2185,11 +2197,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>16.8986873626709</v>
+        <v>16.89868354797363</v>
       </c>
       <c r="C77" t="n">
         <v>23.64999961853027</v>
@@ -2214,11 +2226,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.5478687286377</v>
+        <v>14.54787635803223</v>
       </c>
       <c r="C78" t="n">
         <v>20.36000061035156</v>
@@ -2243,11 +2255,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.68398571014404</v>
+        <v>15.68397521972656</v>
       </c>
       <c r="C79" t="n">
         <v>21.95000076293945</v>
@@ -2272,11 +2284,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.30180835723877</v>
+        <v>15.30180168151855</v>
       </c>
       <c r="C80" t="n">
         <v>21.28000068664551</v>
@@ -2301,11 +2313,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>16.20783615112305</v>
+        <v>16.20783996582031</v>
       </c>
       <c r="C81" t="n">
         <v>22.54000091552734</v>
@@ -2330,11 +2342,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>16.26536178588867</v>
+        <v>16.26535987854004</v>
       </c>
       <c r="C82" t="n">
         <v>22.6200008392334</v>
@@ -2359,11 +2371,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.86252975463867</v>
+        <v>17.86253547668457</v>
       </c>
       <c r="C83" t="n">
         <v>24.70999908447266</v>
@@ -2388,11 +2400,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>17.30591011047363</v>
+        <v>17.3059139251709</v>
       </c>
       <c r="C84" t="n">
         <v>23.94000053405762</v>
@@ -2417,11 +2429,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>18.57819366455078</v>
+        <v>18.57819175720215</v>
       </c>
       <c r="C85" t="n">
         <v>25.70000076293945</v>
@@ -2446,11 +2458,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.72884178161621</v>
+        <v>19.72884750366211</v>
       </c>
       <c r="C86" t="n">
         <v>27.15999984741211</v>
@@ -2475,11 +2487,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>19.71431159973145</v>
+        <v>19.71431732177734</v>
       </c>
       <c r="C87" t="n">
         <v>27.13999938964844</v>
@@ -2504,7 +2516,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2533,11 +2545,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.60982513427734</v>
+        <v>20.60982131958008</v>
       </c>
       <c r="C89" t="n">
         <v>28.21999931335449</v>
@@ -2562,11 +2574,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>21.95362854003906</v>
+        <v>21.95362663269043</v>
       </c>
       <c r="C90" t="n">
         <v>30.05999946594238</v>
@@ -2591,11 +2603,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>20.48566818237305</v>
+        <v>20.48566627502441</v>
       </c>
       <c r="C91" t="n">
         <v>28.04999923706055</v>
@@ -2620,11 +2632,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>23.07722854614258</v>
+        <v>23.07723236083984</v>
       </c>
       <c r="C92" t="n">
         <v>31.45000076293945</v>
@@ -2649,11 +2661,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>21.82247352600098</v>
+        <v>21.82247543334961</v>
       </c>
       <c r="C93" t="n">
         <v>29.73999977111816</v>
@@ -2678,7 +2690,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2736,11 +2748,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>24.84623718261719</v>
+        <v>24.84623908996582</v>
       </c>
       <c r="C96" t="n">
         <v>33.70000076293945</v>
@@ -2765,11 +2777,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>25.76045989990234</v>
+        <v>25.76045417785645</v>
       </c>
       <c r="C97" t="n">
         <v>34.93999862670898</v>
@@ -2794,11 +2806,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>23.67358779907227</v>
+        <v>23.67359161376953</v>
       </c>
       <c r="C98" t="n">
         <v>31.95999908447266</v>
@@ -2823,11 +2835,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.70322036743164</v>
+        <v>23.70321846008301</v>
       </c>
       <c r="C99" t="n">
         <v>32</v>
@@ -2852,11 +2864,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>26.14019966125488</v>
+        <v>26.14020156860352</v>
       </c>
       <c r="C100" t="n">
         <v>35.29000091552734</v>
@@ -2881,11 +2893,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>25.21538352966309</v>
+        <v>25.21537971496582</v>
       </c>
       <c r="C101" t="n">
         <v>33.86999893188477</v>
@@ -2910,7 +2922,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2939,11 +2951,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>27.90294075012207</v>
+        <v>27.9029483795166</v>
       </c>
       <c r="C103" t="n">
         <v>37.47999954223633</v>
@@ -2968,11 +2980,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.18910026550293</v>
+        <v>29.18910217285156</v>
       </c>
       <c r="C104" t="n">
         <v>39.04000091552734</v>
@@ -2997,11 +3009,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>29.29375457763672</v>
+        <v>29.29376411437988</v>
       </c>
       <c r="C105" t="n">
         <v>39.18000030517578</v>
@@ -3026,11 +3038,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>28.95731353759766</v>
+        <v>28.95730972290039</v>
       </c>
       <c r="C106" t="n">
         <v>38.72999954223633</v>
@@ -3055,11 +3067,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>29.08538436889648</v>
+        <v>29.08537864685059</v>
       </c>
       <c r="C107" t="n">
         <v>38.72000122070312</v>
@@ -3084,11 +3096,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>30.06941604614258</v>
+        <v>30.06941223144531</v>
       </c>
       <c r="C108" t="n">
         <v>40.02999877929688</v>
@@ -3113,11 +3125,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.47503852844238</v>
+        <v>30.47504806518555</v>
       </c>
       <c r="C109" t="n">
         <v>40.56999969482422</v>
@@ -3142,11 +3154,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>27.1689453125</v>
+        <v>27.16894149780273</v>
       </c>
       <c r="C110" t="n">
         <v>36</v>
@@ -3171,11 +3183,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.53867149353027</v>
+        <v>29.53868293762207</v>
       </c>
       <c r="C111" t="n">
         <v>39.13999938964844</v>
@@ -3200,11 +3212,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>30.36884117126465</v>
+        <v>30.36884307861328</v>
       </c>
       <c r="C112" t="n">
         <v>40.2400016784668</v>
@@ -3229,11 +3241,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>32.08092498779297</v>
+        <v>32.08093643188477</v>
       </c>
       <c r="C113" t="n">
         <v>42.34000015258789</v>
@@ -3258,11 +3270,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>32.85378265380859</v>
+        <v>32.85379409790039</v>
       </c>
       <c r="C114" t="n">
         <v>43.36000061035156</v>
@@ -3287,11 +3299,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>31.80060386657715</v>
+        <v>31.80059242248535</v>
       </c>
       <c r="C115" t="n">
         <v>41.97000122070312</v>
@@ -3316,11 +3328,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.01228332519531</v>
+        <v>33.01228713989258</v>
       </c>
       <c r="C116" t="n">
         <v>43.40000152587891</v>
@@ -3345,11 +3357,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>30.2739315032959</v>
+        <v>30.27394485473633</v>
       </c>
       <c r="C117" t="n">
         <v>39.79999923706055</v>
@@ -3374,11 +3386,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.77952194213867</v>
+        <v>29.77951049804688</v>
       </c>
       <c r="C118" t="n">
         <v>39.15000152587891</v>
@@ -3403,11 +3415,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.80668067932129</v>
+        <v>31.80668830871582</v>
       </c>
       <c r="C119" t="n">
         <v>41.65000152587891</v>
@@ -3432,11 +3444,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>33.47912979125977</v>
+        <v>33.4791145324707</v>
       </c>
       <c r="C120" t="n">
         <v>43.84000015258789</v>
@@ -3461,11 +3473,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>31.47833061218262</v>
+        <v>31.47830772399902</v>
       </c>
       <c r="C121" t="n">
         <v>41.22000122070312</v>
@@ -3490,11 +3502,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>27.79356575012207</v>
+        <v>27.7935676574707</v>
       </c>
       <c r="C122" t="n">
         <v>36.22000122070312</v>
@@ -3519,11 +3531,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>27.15667343139648</v>
+        <v>27.15665626525879</v>
       </c>
       <c r="C123" t="n">
         <v>35.38999938964844</v>
@@ -3548,11 +3560,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>28.26165771484375</v>
+        <v>28.26165962219238</v>
       </c>
       <c r="C124" t="n">
         <v>36.83000183105469</v>
@@ -3577,11 +3589,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>31.0080394744873</v>
+        <v>31.00804710388184</v>
       </c>
       <c r="C125" t="n">
         <v>40.2400016784668</v>
@@ -3606,11 +3618,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.41049194335938</v>
+        <v>32.41048049926758</v>
       </c>
       <c r="C126" t="n">
         <v>42.06000137329102</v>
@@ -3635,11 +3647,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>29.93694305419922</v>
+        <v>29.93693542480469</v>
       </c>
       <c r="C127" t="n">
         <v>38.84999847412109</v>
@@ -3664,11 +3676,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>30.50627899169922</v>
+        <v>30.50628089904785</v>
       </c>
       <c r="C128" t="n">
         <v>39.40000152587891</v>
@@ -3693,11 +3705,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>32.26387405395508</v>
+        <v>32.26387023925781</v>
       </c>
       <c r="C129" t="n">
         <v>41.66999816894531</v>
@@ -3722,11 +3734,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.8779296875</v>
+        <v>30.87793159484863</v>
       </c>
       <c r="C130" t="n">
         <v>39.88000106811523</v>
@@ -3751,11 +3763,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>33.64900970458984</v>
+        <v>33.64900207519531</v>
       </c>
       <c r="C131" t="n">
         <v>43.27000045776367</v>
@@ -3780,11 +3792,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>36.87626266479492</v>
+        <v>36.87625885009766</v>
       </c>
       <c r="C132" t="n">
         <v>47.41999816894531</v>
@@ -3809,11 +3821,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>36.84515762329102</v>
+        <v>36.84516143798828</v>
       </c>
       <c r="C133" t="n">
         <v>47.38000106811523</v>
@@ -3838,11 +3850,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>34.93197631835938</v>
+        <v>34.93197250366211</v>
       </c>
       <c r="C134" t="n">
         <v>44.72999954223633</v>
@@ -3867,11 +3879,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>36.81406402587891</v>
+        <v>36.81405258178711</v>
       </c>
       <c r="C135" t="n">
         <v>47.13999938964844</v>
@@ -3896,11 +3908,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>36.88433837890625</v>
+        <v>36.88435363769531</v>
       </c>
       <c r="C136" t="n">
         <v>47.22999954223633</v>
@@ -3925,7 +3937,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3954,11 +3966,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>36.94712448120117</v>
+        <v>36.94710159301758</v>
       </c>
       <c r="C138" t="n">
         <v>47.11999893188477</v>
@@ -3983,11 +3995,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>40.00513076782227</v>
+        <v>40.00512313842773</v>
       </c>
       <c r="C139" t="n">
         <v>51.02000045776367</v>
@@ -4012,11 +4024,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.77082443237305</v>
+        <v>41.77083206176758</v>
       </c>
       <c r="C140" t="n">
         <v>53.02999877929688</v>
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>41.18006134033203</v>
+        <v>41.18006896972656</v>
       </c>
       <c r="C141" t="n">
         <v>52.27999877929688</v>
@@ -4070,11 +4082,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>41.7629508972168</v>
+        <v>41.76294326782227</v>
       </c>
       <c r="C142" t="n">
         <v>53.02000045776367</v>
@@ -4099,11 +4111,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>40.71370315551758</v>
+        <v>40.71369171142578</v>
       </c>
       <c r="C143" t="n">
         <v>51.45000076293945</v>
@@ -4128,11 +4140,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>43.3171501159668</v>
+        <v>43.31715774536133</v>
       </c>
       <c r="C144" t="n">
         <v>54.7400016784668</v>
@@ -4157,11 +4169,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>42.62079238891602</v>
+        <v>42.62078475952148</v>
       </c>
       <c r="C145" t="n">
         <v>53.86000061035156</v>
@@ -4186,7 +4198,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4215,7 +4227,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4244,7 +4256,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.50379943847656</v>
+        <v>43.50380325317383</v>
       </c>
       <c r="C149" t="n">
         <v>54.5099983215332</v>
@@ -4302,7 +4314,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4331,7 +4343,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4360,11 +4372,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>42.89868927001953</v>
+        <v>42.898681640625</v>
       </c>
       <c r="C152" t="n">
         <v>53.47000122070312</v>
@@ -4389,11 +4401,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.83966445922852</v>
+        <v>41.83967208862305</v>
       </c>
       <c r="C153" t="n">
         <v>52.15000152587891</v>
@@ -4418,11 +4430,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>40.90900802612305</v>
+        <v>40.90900039672852</v>
       </c>
       <c r="C154" t="n">
         <v>50.9900016784668</v>
@@ -4447,11 +4459,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>38.2078857421875</v>
+        <v>38.20788955688477</v>
       </c>
       <c r="C155" t="n">
         <v>47.33000183105469</v>
@@ -4476,11 +4488,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>41.42079925537109</v>
+        <v>41.42079162597656</v>
       </c>
       <c r="C156" t="n">
         <v>51.31000137329102</v>
@@ -4505,7 +4517,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4534,11 +4546,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>42.45747375488281</v>
+        <v>42.45748519897461</v>
       </c>
       <c r="C158" t="n">
         <v>52.31999969482422</v>
@@ -4563,11 +4575,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>42.58732223510742</v>
+        <v>42.58731079101562</v>
       </c>
       <c r="C159" t="n">
         <v>52.47999954223633</v>
@@ -4592,11 +4604,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>40.92375183105469</v>
+        <v>40.92374801635742</v>
       </c>
       <c r="C160" t="n">
         <v>50.43000030517578</v>
@@ -4621,11 +4633,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>40.53264999389648</v>
+        <v>40.53265380859375</v>
       </c>
       <c r="C161" t="n">
         <v>49.65999984741211</v>
@@ -4650,11 +4662,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>34.84371948242188</v>
+        <v>34.84371566772461</v>
       </c>
       <c r="C162" t="n">
         <v>42.68999862670898</v>
@@ -4679,7 +4691,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4708,7 +4720,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4737,11 +4749,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>34.55603790283203</v>
+        <v>34.5560417175293</v>
       </c>
       <c r="C165" t="n">
         <v>42.06000137329102</v>
@@ -4766,7 +4778,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4795,11 +4807,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>38.66830444335938</v>
+        <v>38.66830825805664</v>
       </c>
       <c r="C167" t="n">
         <v>46.75</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>40.50453186035156</v>
+        <v>40.50453567504883</v>
       </c>
       <c r="C168" t="n">
         <v>48.97000122070312</v>
@@ -4853,11 +4865,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.62942886352539</v>
+        <v>41.62942123413086</v>
       </c>
       <c r="C169" t="n">
         <v>50.33000183105469</v>
@@ -4882,11 +4894,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>37.28466796875</v>
+        <v>37.28467559814453</v>
       </c>
       <c r="C170" t="n">
         <v>44.77999877929688</v>
@@ -4911,7 +4923,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4940,7 +4952,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4969,11 +4981,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>31.52984809875488</v>
+        <v>31.52985191345215</v>
       </c>
       <c r="C173" t="n">
         <v>37.54000091552734</v>
@@ -4998,11 +5010,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.21907615661621</v>
+        <v>31.21907043457031</v>
       </c>
       <c r="C174" t="n">
         <v>37.16999816894531</v>
@@ -5027,11 +5039,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>32.46212768554688</v>
+        <v>32.46213150024414</v>
       </c>
       <c r="C175" t="n">
         <v>38.65000152587891</v>
@@ -5056,11 +5068,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>30.3680534362793</v>
+        <v>30.3680477142334</v>
       </c>
       <c r="C176" t="n">
         <v>35.84999847412109</v>
@@ -5085,7 +5097,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5114,11 +5126,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>29.08895111083984</v>
+        <v>29.08894920349121</v>
       </c>
       <c r="C178" t="n">
         <v>34.34000015258789</v>
@@ -5143,11 +5155,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>29.3536319732666</v>
+        <v>29.35363960266113</v>
       </c>
       <c r="C179" t="n">
         <v>34.36000061035156</v>
@@ -5172,11 +5184,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>33.42008590698242</v>
+        <v>33.42008972167969</v>
       </c>
       <c r="C180" t="n">
         <v>39.11999893188477</v>
@@ -5201,11 +5213,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>36.25635147094727</v>
+        <v>36.25634765625</v>
       </c>
       <c r="C181" t="n">
         <v>42.43999862670898</v>
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>34.28787612915039</v>
+        <v>34.28786468505859</v>
       </c>
       <c r="C182" t="n">
         <v>39.83000183105469</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>36.29365158081055</v>
+        <v>36.29365539550781</v>
       </c>
       <c r="C183" t="n">
         <v>42.15999984741211</v>
@@ -5288,7 +5300,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5317,11 +5329,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>43.21793746948242</v>
+        <v>43.21792984008789</v>
       </c>
       <c r="C185" t="n">
         <v>49.88000106811523</v>
@@ -5346,11 +5358,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>45.12409973144531</v>
+        <v>45.12410736083984</v>
       </c>
       <c r="C186" t="n">
         <v>52.08000183105469</v>
@@ -5375,11 +5387,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>44.38761520385742</v>
+        <v>44.38762283325195</v>
       </c>
       <c r="C187" t="n">
         <v>51.22999954223633</v>
@@ -5404,7 +5416,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5433,11 +5445,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>48.17249298095703</v>
+        <v>48.17248916625977</v>
       </c>
       <c r="C189" t="n">
         <v>55.22000122070312</v>
@@ -5462,11 +5474,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>45.22386169433594</v>
+        <v>45.22385406494141</v>
       </c>
       <c r="C190" t="n">
         <v>51.84000015258789</v>
@@ -5491,11 +5503,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>51.9416389465332</v>
+        <v>51.94163513183594</v>
       </c>
       <c r="C191" t="n">
         <v>59.20000076293945</v>
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>48.07234573364258</v>
+        <v>48.07235336303711</v>
       </c>
       <c r="C192" t="n">
         <v>54.79000091552734</v>
@@ -5549,7 +5561,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5578,11 +5590,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>52.29892730712891</v>
+        <v>52.29892349243164</v>
       </c>
       <c r="C194" t="n">
         <v>59.2599983215332</v>
@@ -5607,11 +5619,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>46.90664291381836</v>
+        <v>46.90664672851562</v>
       </c>
       <c r="C195" t="n">
         <v>53.15000152587891</v>
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>43.80012893676758</v>
+        <v>43.80011749267578</v>
       </c>
       <c r="C196" t="n">
         <v>49.63000106811523</v>
@@ -5665,11 +5677,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>37.41340637207031</v>
+        <v>37.41340255737305</v>
       </c>
       <c r="C197" t="n">
         <v>42.06000137329102</v>
@@ -5694,11 +5706,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>41.46073913574219</v>
+        <v>41.46073532104492</v>
       </c>
       <c r="C198" t="n">
         <v>46.61000061035156</v>
@@ -5723,11 +5735,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>37.1020622253418</v>
+        <v>37.10206985473633</v>
       </c>
       <c r="C199" t="n">
         <v>41.70999908447266</v>
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>38.99053192138672</v>
+        <v>38.99052810668945</v>
       </c>
       <c r="C200" t="n">
         <v>43.45999908447266</v>
@@ -5781,11 +5793,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>37.25901031494141</v>
+        <v>37.25900650024414</v>
       </c>
       <c r="C201" t="n">
         <v>41.52999877929688</v>
@@ -5810,11 +5822,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.55856704711914</v>
+        <v>34.55855941772461</v>
       </c>
       <c r="C202" t="n">
         <v>38.52000045776367</v>
@@ -5839,11 +5851,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>38.11840438842773</v>
+        <v>38.11839294433594</v>
       </c>
       <c r="C203" t="n">
         <v>42.11000061035156</v>
@@ -5868,11 +5880,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>41.54914093017578</v>
+        <v>41.54914855957031</v>
       </c>
       <c r="C204" t="n">
         <v>45.90000152587891</v>
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>41.20516586303711</v>
+        <v>41.20516967773438</v>
       </c>
       <c r="C205" t="n">
         <v>45.52000045776367</v>
@@ -5926,11 +5938,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>46.12533950805664</v>
+        <v>46.12533187866211</v>
       </c>
       <c r="C206" t="n">
         <v>50.56999969482422</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.40809631347656</v>
+        <v>46.40808486938477</v>
       </c>
       <c r="C207" t="n">
         <v>50.88000106811523</v>
@@ -5984,7 +5996,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6042,11 +6054,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>36.99431991577148</v>
+        <v>36.99430847167969</v>
       </c>
       <c r="C210" t="n">
         <v>40.20000076293945</v>
@@ -6071,11 +6083,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>40.96981430053711</v>
+        <v>40.96981811523438</v>
       </c>
       <c r="C211" t="n">
         <v>44.52000045776367</v>
@@ -6100,11 +6112,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.13070678710938</v>
+        <v>42.13071441650391</v>
       </c>
       <c r="C212" t="n">
         <v>45.36000061035156</v>
@@ -6129,11 +6141,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>41.67559814453125</v>
+        <v>41.67559051513672</v>
       </c>
       <c r="C213" t="n">
         <v>44.86999893188477</v>
@@ -6158,11 +6170,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>39.61364364624023</v>
+        <v>39.61363983154297</v>
       </c>
       <c r="C214" t="n">
         <v>42.65000152587891</v>
@@ -6187,11 +6199,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>39.87449264526367</v>
+        <v>39.87449645996094</v>
       </c>
       <c r="C215" t="n">
         <v>42.5</v>
@@ -6216,11 +6228,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>45.33495712280273</v>
+        <v>45.3349609375</v>
       </c>
       <c r="C216" t="n">
         <v>48.31999969482422</v>
@@ -6245,11 +6257,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>48.83451843261719</v>
+        <v>48.83452606201172</v>
       </c>
       <c r="C217" t="n">
         <v>52.04999923706055</v>
@@ -6274,7 +6286,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6303,11 +6315,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>53.0326042175293</v>
+        <v>53.03260040283203</v>
       </c>
       <c r="C219" t="n">
         <v>56.09000015258789</v>
@@ -6332,11 +6344,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>54.47919845581055</v>
+        <v>54.47919082641602</v>
       </c>
       <c r="C220" t="n">
         <v>57.61999893188477</v>
@@ -6361,11 +6373,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>53.80072402954102</v>
+        <v>53.80071640014648</v>
       </c>
       <c r="C221" t="n">
         <v>56.4900016784668</v>
@@ -6390,11 +6402,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>56.77218627929688</v>
+        <v>56.77218246459961</v>
       </c>
       <c r="C222" t="n">
         <v>59.61000061035156</v>
@@ -6419,11 +6431,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>57.03886032104492</v>
+        <v>57.03884887695312</v>
       </c>
       <c r="C223" t="n">
         <v>59.88999938964844</v>
@@ -6448,11 +6460,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>62.44038772583008</v>
+        <v>62.44038391113281</v>
       </c>
       <c r="C224" t="n">
         <v>65.06999969482422</v>
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6506,11 +6518,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>68.95599365234375</v>
+        <v>68.95597839355469</v>
       </c>
       <c r="C226" t="n">
         <v>71.86000061035156</v>
@@ -6535,11 +6547,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>72.76058197021484</v>
+        <v>72.76057434082031</v>
       </c>
       <c r="C227" t="n">
         <v>75.36000061035156</v>
@@ -6564,11 +6576,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>79.04603576660156</v>
+        <v>79.04602813720703</v>
       </c>
       <c r="C228" t="n">
         <v>81.87000274658203</v>
@@ -6593,7 +6605,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6622,11 +6634,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>83.42301940917969</v>
+        <v>83.42301177978516</v>
       </c>
       <c r="C230" t="n">
         <v>85.93000030517578</v>
@@ -6651,11 +6663,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>86.35489654541016</v>
+        <v>86.35491180419922</v>
       </c>
       <c r="C231" t="n">
         <v>88.94999694824219</v>
@@ -6680,11 +6692,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>81.42312622070312</v>
+        <v>81.42310333251953</v>
       </c>
       <c r="C232" t="n">
         <v>83.87000274658203</v>
@@ -6709,7 +6721,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6738,7 +6750,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6767,7 +6779,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6825,11 +6837,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>103.7040252685547</v>
+        <v>103.7040328979492</v>
       </c>
       <c r="C237" t="n">
         <v>105.5999984741211</v>
@@ -6854,7 +6866,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6883,7 +6895,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6912,11 +6924,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>110.6302795410156</v>
+        <v>110.6302871704102</v>
       </c>
       <c r="C240" t="n">
         <v>112.0999984741211</v>
@@ -6941,11 +6953,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>114.5679779052734</v>
+        <v>114.5679702758789</v>
       </c>
       <c r="C241" t="n">
         <v>116.0899963378906</v>
@@ -6970,11 +6982,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>118.9219741821289</v>
+        <v>118.9219818115234</v>
       </c>
       <c r="C242" t="n">
         <v>119.9199981689453</v>
@@ -6999,11 +7011,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>118.1587982177734</v>
+        <v>118.158805847168</v>
       </c>
       <c r="C243" t="n">
         <v>119.0999984741211</v>
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7057,7 +7069,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7086,7 +7098,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7115,7 +7127,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7144,7 +7156,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7173,7 +7185,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7202,32 +7214,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>149.5099945068359</v>
+        <v>150.1900024414062</v>
       </c>
       <c r="C250" t="n">
-        <v>149.5099945068359</v>
+        <v>150.1900024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>61301200</v>
+        <v>64845700</v>
       </c>
       <c r="E250" t="n">
         <v>8.580000000000002</v>
       </c>
       <c r="F250" t="n">
-        <v>17.42540728517901</v>
+        <v>17.50466228920818</v>
       </c>
       <c r="G250" t="n">
         <v>678504142</v>
       </c>
       <c r="H250" t="n">
-        <v>101443150543.2854</v>
+        <v>101904538743.4843</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09034756931520692</v>
+        <v>0.09557156100603435</v>
       </c>
     </row>
   </sheetData>
@@ -7259,75 +7271,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7564,7 +7576,7 @@
       <c r="I7" t="n">
         <v>-1.16</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="K7" t="n">
@@ -7577,13 +7589,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="I8" t="n">
         <v>-0.9800000000000002</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="K8" t="n">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I9" t="n">
         <v>-0.5900000000000001</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="K9" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I10" t="n">
         <v>1.97</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="K10" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I11" t="n">
         <v>2.05</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I12" t="n">
         <v>2.09</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K12" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I13" t="n">
         <v>2.14</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K13" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I14" t="n">
         <v>2.16</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K14" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I15" t="n">
         <v>2.03</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K15" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I16" t="n">
         <v>2.05</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K16" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I17" t="n">
         <v>1.85</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K17" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I18" t="n">
         <v>1.93</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K18" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I19" t="n">
         <v>2.03</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I20" t="n">
         <v>1.28</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K20" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K21" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I22" t="n">
         <v>1.81</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K22" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I23" t="n">
         <v>1.74</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K23" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I24" t="n">
         <v>2.54</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="K24" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I25" t="n">
         <v>2.31</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="K25" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I26" t="n">
         <v>2.42</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K26" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I27" t="n">
         <v>2.15</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I28" t="n">
         <v>2.25</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K28" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I29" t="n">
         <v>2.5</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K29" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I30" t="n">
         <v>2.31</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K30" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I31" t="n">
         <v>2.71</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I32" t="n">
         <v>2.77</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K32" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I33" t="n">
         <v>2.79</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="K33" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I34" t="n">
         <v>2.95</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="K34" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I35" t="n">
         <v>3.15</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K35" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I36" t="n">
         <v>3.25</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="K36" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I37" t="n">
         <v>3.38</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I38" t="n">
         <v>3.42</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K38" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I39" t="n">
         <v>3.72</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K39" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I40" t="n">
         <v>3.990000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K40" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I41" t="n">
         <v>4.140000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K41" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I42" t="n">
         <v>4.260000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K42" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I43" t="n">
         <v>4.04</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K43" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I44" t="n">
         <v>3.88</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I45" t="n">
         <v>3.86</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I46" t="n">
         <v>3.87</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K46" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I47" t="n">
         <v>4.51</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K47" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I48" t="n">
         <v>4.619999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K48" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I49" t="n">
         <v>4.62</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I50" t="n">
         <v>4.529999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K50" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I51" t="n">
         <v>3.83</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I52" t="n">
         <v>3.75</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I53" t="n">
         <v>3.87</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K53" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I54" t="n">
         <v>3.93</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K54" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I55" t="n">
         <v>4.14</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K55" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I56" t="n">
         <v>4.03</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="K56" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I57" t="n">
         <v>3.93</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K57" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I58" t="n">
         <v>3.28</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="K58" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I59" t="n">
         <v>2.9</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K59" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I60" t="n">
         <v>3.16</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K60" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I61" t="n">
         <v>3.43</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I62" t="n">
         <v>4.26</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K62" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I63" t="n">
         <v>3.870000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K63" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I64" t="n">
         <v>4</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10199,13 +10211,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10232,7 +10244,7 @@
       <c r="I65" t="n">
         <v>4.220000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K65" t="n">
@@ -10245,13 +10257,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10278,7 +10290,7 @@
       <c r="I66" t="n">
         <v>4.5</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10291,13 +10303,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10324,7 +10336,7 @@
       <c r="I67" t="n">
         <v>5.800000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K67" t="n">
@@ -10337,13 +10349,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10370,7 +10382,7 @@
       <c r="I68" t="n">
         <v>6.130000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K68" t="n">
@@ -10383,13 +10395,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10416,7 +10428,7 @@
       <c r="I69" t="n">
         <v>6.540000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10429,13 +10441,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10462,7 +10474,7 @@
       <c r="I70" t="n">
         <v>6.920000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10475,13 +10487,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10508,7 +10520,7 @@
       <c r="I71" t="n">
         <v>7.400000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10521,13 +10533,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10554,7 +10566,7 @@
       <c r="I72" t="n">
         <v>8.06</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10567,13 +10579,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10600,7 +10612,7 @@
       <c r="I73" t="n">
         <v>8.580000000000002</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K73" t="n">
@@ -10637,52 +10649,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C10" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C11" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C12" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C13" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C14" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C15" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C17" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C18" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C19" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C20" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="C21" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41862</v>
       </c>
       <c r="C22" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C23" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C25" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C26" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C27" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C28" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C29" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="C30" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="C31" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C32" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="C33" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C35" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C36" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C37" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C38" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C40" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C41" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C43" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C47" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C51" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C52" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C53" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C54" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="C55" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C56" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C57" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C59" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C60" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C61" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C64" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12791,10 +12803,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12823,10 +12835,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12855,10 +12867,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12905,12 +12917,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BNY.xlsx
+++ b/salidas/empresas/BNY.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>21.10313034057617</v>
+        <v>21.10311889648438</v>
       </c>
       <c r="C2" t="n">
         <v>33.71846389770508</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.7152099609375</v>
+        <v>22.71520614624023</v>
       </c>
       <c r="C3" t="n">
         <v>36.29425430297852</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>23.90934944152832</v>
+        <v>23.90935897827148</v>
       </c>
       <c r="C4" t="n">
         <v>38.20224761962891</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.46290969848633</v>
+        <v>23.4629077911377</v>
       </c>
       <c r="C5" t="n">
         <v>37.25885009765625</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1812915802002</v>
+        <v>22.18128967285156</v>
       </c>
       <c r="C6" t="n">
         <v>35.22365951538086</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.49374961853027</v>
+        <v>21.4937572479248</v>
       </c>
       <c r="C7" t="n">
         <v>34.13186264038086</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>22.58400917053223</v>
+        <v>22.5839958190918</v>
       </c>
       <c r="C8" t="n">
         <v>35.62645721435547</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.67808723449707</v>
+        <v>22.67808151245117</v>
       </c>
       <c r="C9" t="n">
         <v>35.77485656738281</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>23.69271850585938</v>
+        <v>23.69271469116211</v>
       </c>
       <c r="C10" t="n">
         <v>37.37545013427734</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.24699974060059</v>
+        <v>23.24699401855469</v>
       </c>
       <c r="C11" t="n">
         <v>36.43205261230469</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.0383472442627</v>
+        <v>24.03835487365723</v>
       </c>
       <c r="C12" t="n">
         <v>37.67224884033203</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.62887763977051</v>
+        <v>26.62886810302734</v>
       </c>
       <c r="C13" t="n">
         <v>41.73203277587891</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.2076587677002</v>
+        <v>27.20767021179199</v>
       </c>
       <c r="C14" t="n">
         <v>42.41043090820312</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>27.62928199768066</v>
+        <v>27.62927436828613</v>
       </c>
       <c r="C15" t="n">
         <v>43.067626953125</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>27.57485961914062</v>
+        <v>27.57487106323242</v>
       </c>
       <c r="C16" t="n">
         <v>42.98282623291016</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.67398452758789</v>
+        <v>27.67397499084473</v>
       </c>
       <c r="C17" t="n">
         <v>42.90862655639648</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>27.72866058349609</v>
+        <v>27.72865867614746</v>
       </c>
       <c r="C18" t="n">
         <v>42.99342727661133</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.33028221130371</v>
+        <v>28.33028030395508</v>
       </c>
       <c r="C19" t="n">
         <v>43.92622375488281</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.59094619750977</v>
+        <v>27.59095001220703</v>
       </c>
       <c r="C20" t="n">
         <v>42.54999923706055</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>26.21626663208008</v>
+        <v>26.21626472473145</v>
       </c>
       <c r="C21" t="n">
         <v>40.43000030517578</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>31.84372901916504</v>
+        <v>31.8437328338623</v>
       </c>
       <c r="C23" t="n">
         <v>48.84999847412109</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.26357078552246</v>
+        <v>31.26355171203613</v>
       </c>
       <c r="C24" t="n">
         <v>47.95999908447266</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.48833274841309</v>
+        <v>30.48831558227539</v>
       </c>
       <c r="C26" t="n">
         <v>46.52000045776367</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.75156593322754</v>
+        <v>28.75155639648438</v>
       </c>
       <c r="C27" t="n">
         <v>43.86999893188477</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.34903717041016</v>
+        <v>27.34904289245605</v>
       </c>
       <c r="C28" t="n">
         <v>41.72999954223633</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>28.69125366210938</v>
+        <v>28.69125175476074</v>
       </c>
       <c r="C29" t="n">
         <v>43.52999877929688</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.35036849975586</v>
+        <v>29.35036087036133</v>
       </c>
       <c r="C30" t="n">
         <v>44.52999877929688</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.93429756164551</v>
+        <v>24.93429565429688</v>
       </c>
       <c r="C31" t="n">
         <v>37.83000183105469</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.96522903442383</v>
+        <v>22.96523094177246</v>
       </c>
       <c r="C33" t="n">
         <v>34.61000061035156</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.19903945922852</v>
+        <v>20.19904518127441</v>
       </c>
       <c r="C36" t="n">
         <v>30.20999908447266</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.94203567504883</v>
+        <v>18.94204139709473</v>
       </c>
       <c r="C37" t="n">
         <v>28.32999992370605</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.43047523498535</v>
+        <v>17.43048667907715</v>
       </c>
       <c r="C38" t="n">
         <v>25.73999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.31671142578125</v>
+        <v>17.31669807434082</v>
       </c>
       <c r="C41" t="n">
         <v>25.47999954223633</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>18.87983703613281</v>
+        <v>18.87983131408691</v>
       </c>
       <c r="C42" t="n">
         <v>27.78000068664551</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>19.91965103149414</v>
+        <v>19.91965293884277</v>
       </c>
       <c r="C43" t="n">
         <v>29.30999946594238</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.64267539978027</v>
+        <v>18.64266014099121</v>
       </c>
       <c r="C44" t="n">
         <v>27.34000015258789</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>19.76777076721191</v>
+        <v>19.76777458190918</v>
       </c>
       <c r="C46" t="n">
         <v>28.98999977111816</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>18.23811721801758</v>
+        <v>18.23811149597168</v>
       </c>
       <c r="C47" t="n">
         <v>26.65999984741211</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.22443389892578</v>
+        <v>18.22443199157715</v>
       </c>
       <c r="C48" t="n">
         <v>26.63999938964844</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.1342945098877</v>
+        <v>19.1342887878418</v>
       </c>
       <c r="C49" t="n">
         <v>27.96999931335449</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.96084213256836</v>
+        <v>19.96084785461426</v>
       </c>
       <c r="C50" t="n">
         <v>29.09000015258789</v>
@@ -1492,7 +1492,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.18910026550293</v>
+        <v>21.1890983581543</v>
       </c>
       <c r="C52" t="n">
         <v>30.8799991607666</v>
@@ -1519,7 +1519,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.423095703125</v>
+        <v>21.42309761047363</v>
       </c>
       <c r="C53" t="n">
         <v>31.1299991607666</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.71854400634766</v>
+        <v>18.71854019165039</v>
       </c>
       <c r="C54" t="n">
         <v>27.20000076293945</v>
@@ -1573,7 +1573,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.99120903015137</v>
+        <v>16.9912109375</v>
       </c>
       <c r="C55" t="n">
         <v>24.69000053405762</v>
@@ -1600,7 +1600,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.31230926513672</v>
+        <v>17.31230354309082</v>
       </c>
       <c r="C56" t="n">
         <v>25.06999969482422</v>
@@ -1627,7 +1627,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.75295257568359</v>
+        <v>16.75295448303223</v>
       </c>
       <c r="C57" t="n">
         <v>24.26000022888184</v>
@@ -1654,7 +1654,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.0443000793457</v>
+        <v>18.0442943572998</v>
       </c>
       <c r="C58" t="n">
         <v>26.1299991607666</v>
@@ -1681,7 +1681,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.36784934997559</v>
+        <v>17.36784553527832</v>
       </c>
       <c r="C59" t="n">
         <v>25.05999946594238</v>
@@ -1708,7 +1708,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>18.70543098449707</v>
+        <v>18.70543670654297</v>
       </c>
       <c r="C60" t="n">
         <v>26.98999977111816</v>
@@ -1737,7 +1737,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.93012428283691</v>
+        <v>20.93012809753418</v>
       </c>
       <c r="C61" t="n">
         <v>30.20000076293945</v>
@@ -1766,7 +1766,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>21.70557594299316</v>
+        <v>21.7055721282959</v>
       </c>
       <c r="C62" t="n">
         <v>31.22999954223633</v>
@@ -1795,7 +1795,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.12176322937012</v>
+        <v>21.12175750732422</v>
       </c>
       <c r="C63" t="n">
         <v>30.38999938964844</v>
@@ -1853,7 +1853,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>20.21946334838867</v>
+        <v>20.21945762634277</v>
       </c>
       <c r="C65" t="n">
         <v>28.95999908447266</v>
@@ -1911,7 +1911,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.88751602172852</v>
+        <v>17.88752174377441</v>
       </c>
       <c r="C67" t="n">
         <v>25.6200008392334</v>
@@ -1940,7 +1940,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>17.62053298950195</v>
+        <v>17.62054252624512</v>
       </c>
       <c r="C68" t="n">
         <v>25.11000061035156</v>
@@ -1969,7 +1969,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.50483512878418</v>
+        <v>14.50484275817871</v>
       </c>
       <c r="C69" t="n">
         <v>20.67000007629395</v>
@@ -1998,7 +1998,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>13.0452299118042</v>
+        <v>13.04522895812988</v>
       </c>
       <c r="C70" t="n">
         <v>18.59000015258789</v>
@@ -2027,7 +2027,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.02609157562256</v>
+        <v>15.02609443664551</v>
       </c>
       <c r="C71" t="n">
         <v>21.28000068664551</v>
@@ -2056,7 +2056,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>13.74096870422363</v>
+        <v>13.74096584320068</v>
       </c>
       <c r="C72" t="n">
         <v>19.45999908447266</v>
@@ -2085,7 +2085,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.0587215423584</v>
+        <v>14.05871772766113</v>
       </c>
       <c r="C73" t="n">
         <v>19.90999984741211</v>
@@ -2114,7 +2114,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>14.30446624755859</v>
+        <v>14.3044605255127</v>
       </c>
       <c r="C74" t="n">
         <v>20.1299991607666</v>
@@ -2143,7 +2143,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.71147441864014</v>
+        <v>15.71146392822266</v>
       </c>
       <c r="C75" t="n">
         <v>22.11000061035156</v>
@@ -2172,7 +2172,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>17.14688873291016</v>
+        <v>17.14688682556152</v>
       </c>
       <c r="C76" t="n">
         <v>24.1299991607666</v>
@@ -2230,7 +2230,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.54787635803223</v>
+        <v>14.54787254333496</v>
       </c>
       <c r="C78" t="n">
         <v>20.36000061035156</v>
@@ -2259,7 +2259,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.68397521972656</v>
+        <v>15.68398094177246</v>
       </c>
       <c r="C79" t="n">
         <v>21.95000076293945</v>
@@ -2288,7 +2288,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.30180168151855</v>
+        <v>15.30180549621582</v>
       </c>
       <c r="C80" t="n">
         <v>21.28000068664551</v>
@@ -2317,7 +2317,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>16.20783996582031</v>
+        <v>16.20783805847168</v>
       </c>
       <c r="C81" t="n">
         <v>22.54000091552734</v>
@@ -2375,7 +2375,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.86253547668457</v>
+        <v>17.86252975463867</v>
       </c>
       <c r="C83" t="n">
         <v>24.70999908447266</v>
@@ -2404,7 +2404,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>17.3059139251709</v>
+        <v>17.3059024810791</v>
       </c>
       <c r="C84" t="n">
         <v>23.94000053405762</v>
@@ -2433,7 +2433,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>18.57819175720215</v>
+        <v>18.57818984985352</v>
       </c>
       <c r="C85" t="n">
         <v>25.70000076293945</v>
@@ -2462,7 +2462,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.72884750366211</v>
+        <v>19.72884178161621</v>
       </c>
       <c r="C86" t="n">
         <v>27.15999984741211</v>
@@ -2491,7 +2491,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>19.71431732177734</v>
+        <v>19.71431350708008</v>
       </c>
       <c r="C87" t="n">
         <v>27.13999938964844</v>
@@ -2520,7 +2520,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>20.33175277709961</v>
+        <v>20.33174705505371</v>
       </c>
       <c r="C88" t="n">
         <v>27.98999977111816</v>
@@ -2549,7 +2549,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.60982131958008</v>
+        <v>20.60982894897461</v>
       </c>
       <c r="C89" t="n">
         <v>28.21999931335449</v>
@@ -2578,7 +2578,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>21.95362663269043</v>
+        <v>21.95362854003906</v>
       </c>
       <c r="C90" t="n">
         <v>30.05999946594238</v>
@@ -2607,7 +2607,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>20.48566627502441</v>
+        <v>20.48566436767578</v>
       </c>
       <c r="C91" t="n">
         <v>28.04999923706055</v>
@@ -2636,7 +2636,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>23.07723236083984</v>
+        <v>23.07722473144531</v>
       </c>
       <c r="C92" t="n">
         <v>31.45000076293945</v>
@@ -2665,7 +2665,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>21.82247543334961</v>
+        <v>21.82247352600098</v>
       </c>
       <c r="C93" t="n">
         <v>29.73999977111816</v>
@@ -2694,7 +2694,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>22.15267181396484</v>
+        <v>22.15267372131348</v>
       </c>
       <c r="C94" t="n">
         <v>30.19000053405762</v>
@@ -2723,7 +2723,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>23.44541168212891</v>
+        <v>23.44541549682617</v>
       </c>
       <c r="C95" t="n">
         <v>31.79999923706055</v>
@@ -2752,7 +2752,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>24.84623908996582</v>
+        <v>24.84623527526855</v>
       </c>
       <c r="C96" t="n">
         <v>33.70000076293945</v>
@@ -2781,7 +2781,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>25.76045417785645</v>
+        <v>25.76046180725098</v>
       </c>
       <c r="C97" t="n">
         <v>34.93999862670898</v>
@@ -2839,7 +2839,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.70321846008301</v>
+        <v>23.70322036743164</v>
       </c>
       <c r="C99" t="n">
         <v>32</v>
@@ -2868,7 +2868,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>26.14020156860352</v>
+        <v>26.14020729064941</v>
       </c>
       <c r="C100" t="n">
         <v>35.29000091552734</v>
@@ -2897,7 +2897,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>25.21537971496582</v>
+        <v>25.21538543701172</v>
       </c>
       <c r="C101" t="n">
         <v>33.86999893188477</v>
@@ -2955,7 +2955,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>27.9029483795166</v>
+        <v>27.90293121337891</v>
       </c>
       <c r="C103" t="n">
         <v>37.47999954223633</v>
@@ -2984,7 +2984,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>29.18910217285156</v>
+        <v>29.18910026550293</v>
       </c>
       <c r="C104" t="n">
         <v>39.04000091552734</v>
@@ -3013,7 +3013,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>29.29376411437988</v>
+        <v>29.29376792907715</v>
       </c>
       <c r="C105" t="n">
         <v>39.18000030517578</v>
@@ -3042,7 +3042,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>28.95730972290039</v>
+        <v>28.95731163024902</v>
       </c>
       <c r="C106" t="n">
         <v>38.72999954223633</v>
@@ -3071,7 +3071,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>29.08537864685059</v>
+        <v>29.08538436889648</v>
       </c>
       <c r="C107" t="n">
         <v>38.72000122070312</v>
@@ -3100,7 +3100,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>30.06941223144531</v>
+        <v>30.06941795349121</v>
       </c>
       <c r="C108" t="n">
         <v>40.02999877929688</v>
@@ -3129,7 +3129,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.47504806518555</v>
+        <v>30.47504997253418</v>
       </c>
       <c r="C109" t="n">
         <v>40.56999969482422</v>
@@ -3158,7 +3158,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>27.16894149780273</v>
+        <v>27.16894721984863</v>
       </c>
       <c r="C110" t="n">
         <v>36</v>
@@ -3187,7 +3187,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.53868293762207</v>
+        <v>29.53868103027344</v>
       </c>
       <c r="C111" t="n">
         <v>39.13999938964844</v>
@@ -3216,7 +3216,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>30.36884307861328</v>
+        <v>30.36883163452148</v>
       </c>
       <c r="C112" t="n">
         <v>40.2400016784668</v>
@@ -3274,7 +3274,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>32.85379409790039</v>
+        <v>32.85378646850586</v>
       </c>
       <c r="C114" t="n">
         <v>43.36000061035156</v>
@@ -3303,7 +3303,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>31.80059242248535</v>
+        <v>31.80059623718262</v>
       </c>
       <c r="C115" t="n">
         <v>41.97000122070312</v>
@@ -3332,7 +3332,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.01228713989258</v>
+        <v>33.01229095458984</v>
       </c>
       <c r="C116" t="n">
         <v>43.40000152587891</v>
@@ -3361,7 +3361,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>30.27394485473633</v>
+        <v>30.27395057678223</v>
       </c>
       <c r="C117" t="n">
         <v>39.79999923706055</v>
@@ -3390,7 +3390,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.77951049804688</v>
+        <v>29.77952003479004</v>
       </c>
       <c r="C118" t="n">
         <v>39.15000152587891</v>
@@ -3419,7 +3419,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.80668830871582</v>
+        <v>31.80668067932129</v>
       </c>
       <c r="C119" t="n">
         <v>41.65000152587891</v>
@@ -3448,7 +3448,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>33.4791145324707</v>
+        <v>33.47910690307617</v>
       </c>
       <c r="C120" t="n">
         <v>43.84000015258789</v>
@@ -3506,7 +3506,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>27.7935676574707</v>
+        <v>27.79356956481934</v>
       </c>
       <c r="C122" t="n">
         <v>36.22000122070312</v>
@@ -3535,7 +3535,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>27.15665626525879</v>
+        <v>27.15666770935059</v>
       </c>
       <c r="C123" t="n">
         <v>35.38999938964844</v>
@@ -3593,7 +3593,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>31.00804710388184</v>
+        <v>31.00803756713867</v>
       </c>
       <c r="C125" t="n">
         <v>40.2400016784668</v>
@@ -3622,7 +3622,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.41048049926758</v>
+        <v>32.41049957275391</v>
       </c>
       <c r="C126" t="n">
         <v>42.06000137329102</v>
@@ -3651,7 +3651,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>29.93693542480469</v>
+        <v>29.93694496154785</v>
       </c>
       <c r="C127" t="n">
         <v>38.84999847412109</v>
@@ -3680,7 +3680,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>30.50628089904785</v>
+        <v>30.50628280639648</v>
       </c>
       <c r="C128" t="n">
         <v>39.40000152587891</v>
@@ -3709,7 +3709,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>32.26387023925781</v>
+        <v>32.26387405395508</v>
       </c>
       <c r="C129" t="n">
         <v>41.66999816894531</v>
@@ -3738,7 +3738,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.87793159484863</v>
+        <v>30.8779296875</v>
       </c>
       <c r="C130" t="n">
         <v>39.88000106811523</v>
@@ -3767,7 +3767,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>33.64900207519531</v>
+        <v>33.64899444580078</v>
       </c>
       <c r="C131" t="n">
         <v>43.27000045776367</v>
@@ -3796,7 +3796,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>36.87625885009766</v>
+        <v>36.87626647949219</v>
       </c>
       <c r="C132" t="n">
         <v>47.41999816894531</v>
@@ -3825,7 +3825,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>36.84516143798828</v>
+        <v>36.84516906738281</v>
       </c>
       <c r="C133" t="n">
         <v>47.38000106811523</v>
@@ -3854,7 +3854,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>34.93197250366211</v>
+        <v>34.93196868896484</v>
       </c>
       <c r="C134" t="n">
         <v>44.72999954223633</v>
@@ -3883,7 +3883,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>36.81405258178711</v>
+        <v>36.81406402587891</v>
       </c>
       <c r="C135" t="n">
         <v>47.13999938964844</v>
@@ -3912,7 +3912,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>36.88435363769531</v>
+        <v>36.88434219360352</v>
       </c>
       <c r="C136" t="n">
         <v>47.22999954223633</v>
@@ -3941,7 +3941,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.90006637573242</v>
+        <v>36.90005493164062</v>
       </c>
       <c r="C137" t="n">
         <v>47.06000137329102</v>
@@ -3999,7 +3999,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>40.00512313842773</v>
+        <v>40.005126953125</v>
       </c>
       <c r="C139" t="n">
         <v>51.02000045776367</v>
@@ -4028,7 +4028,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.77083206176758</v>
+        <v>41.77083969116211</v>
       </c>
       <c r="C140" t="n">
         <v>53.02999877929688</v>
@@ -4057,7 +4057,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>41.18006896972656</v>
+        <v>41.18006134033203</v>
       </c>
       <c r="C141" t="n">
         <v>52.27999877929688</v>
@@ -4086,7 +4086,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>41.76294326782227</v>
+        <v>41.7629508972168</v>
       </c>
       <c r="C142" t="n">
         <v>53.02000045776367</v>
@@ -4144,7 +4144,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>43.31715774536133</v>
+        <v>43.31714630126953</v>
       </c>
       <c r="C144" t="n">
         <v>54.7400016784668</v>
@@ -4173,7 +4173,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>42.62078475952148</v>
+        <v>42.62078857421875</v>
       </c>
       <c r="C145" t="n">
         <v>53.86000061035156</v>
@@ -4202,7 +4202,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>45.05530166625977</v>
+        <v>45.05529403686523</v>
       </c>
       <c r="C146" t="n">
         <v>56.70000076293945</v>
@@ -4231,7 +4231,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>45.31752395629883</v>
+        <v>45.31753540039062</v>
       </c>
       <c r="C147" t="n">
         <v>57.02999877929688</v>
@@ -4260,7 +4260,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>40.94707870483398</v>
+        <v>40.94708251953125</v>
       </c>
       <c r="C148" t="n">
         <v>51.52999877929688</v>
@@ -4289,7 +4289,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>43.50380325317383</v>
+        <v>43.50379943847656</v>
       </c>
       <c r="C149" t="n">
         <v>54.5099983215332</v>
@@ -4318,7 +4318,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.69534301757812</v>
+        <v>43.69533920288086</v>
       </c>
       <c r="C150" t="n">
         <v>54.75</v>
@@ -4347,7 +4347,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>43.04091644287109</v>
+        <v>43.04092025756836</v>
       </c>
       <c r="C151" t="n">
         <v>53.93000030517578</v>
@@ -4376,7 +4376,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>42.898681640625</v>
+        <v>42.89868545532227</v>
       </c>
       <c r="C152" t="n">
         <v>53.47000122070312</v>
@@ -4405,7 +4405,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>41.83967208862305</v>
+        <v>41.83964920043945</v>
       </c>
       <c r="C153" t="n">
         <v>52.15000152587891</v>
@@ -4434,7 +4434,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>40.90900039672852</v>
+        <v>40.90899658203125</v>
       </c>
       <c r="C154" t="n">
         <v>50.9900016784668</v>
@@ -4463,7 +4463,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>38.20788955688477</v>
+        <v>38.20787811279297</v>
       </c>
       <c r="C155" t="n">
         <v>47.33000183105469</v>
@@ -4492,7 +4492,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>41.42079162597656</v>
+        <v>41.42079925537109</v>
       </c>
       <c r="C156" t="n">
         <v>51.31000137329102</v>
@@ -4521,7 +4521,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>37.99798583984375</v>
+        <v>37.99798965454102</v>
       </c>
       <c r="C157" t="n">
         <v>47.06999969482422</v>
@@ -4550,7 +4550,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>42.45748519897461</v>
+        <v>42.45747756958008</v>
       </c>
       <c r="C158" t="n">
         <v>52.31999969482422</v>
@@ -4579,7 +4579,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>42.58731079101562</v>
+        <v>42.58731842041016</v>
       </c>
       <c r="C159" t="n">
         <v>52.47999954223633</v>
@@ -4608,7 +4608,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>40.92374801635742</v>
+        <v>40.92374420166016</v>
       </c>
       <c r="C160" t="n">
         <v>50.43000030517578</v>
@@ -4637,7 +4637,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>40.53265380859375</v>
+        <v>40.53265762329102</v>
       </c>
       <c r="C161" t="n">
         <v>49.65999984741211</v>
@@ -4666,7 +4666,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>34.84371566772461</v>
+        <v>34.84370803833008</v>
       </c>
       <c r="C162" t="n">
         <v>42.68999862670898</v>
@@ -4724,7 +4724,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>38.54895782470703</v>
+        <v>38.54895401000977</v>
       </c>
       <c r="C164" t="n">
         <v>46.91999816894531</v>
@@ -4782,7 +4782,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>37.14403533935547</v>
+        <v>37.14404296875</v>
       </c>
       <c r="C166" t="n">
         <v>45.20999908447266</v>
@@ -4811,7 +4811,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>38.66830825805664</v>
+        <v>38.66831207275391</v>
       </c>
       <c r="C167" t="n">
         <v>46.75</v>
@@ -4869,7 +4869,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.62942123413086</v>
+        <v>41.62942886352539</v>
       </c>
       <c r="C169" t="n">
         <v>50.33000183105469</v>
@@ -4898,7 +4898,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>37.28467559814453</v>
+        <v>37.28466415405273</v>
       </c>
       <c r="C170" t="n">
         <v>44.77999877929688</v>
@@ -4927,7 +4927,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>33.22149658203125</v>
+        <v>33.22150039672852</v>
       </c>
       <c r="C171" t="n">
         <v>39.90000152587891</v>
@@ -4985,7 +4985,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>31.52985191345215</v>
+        <v>31.52984237670898</v>
       </c>
       <c r="C173" t="n">
         <v>37.54000091552734</v>
@@ -5014,7 +5014,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.21907043457031</v>
+        <v>31.21907615661621</v>
       </c>
       <c r="C174" t="n">
         <v>37.16999816894531</v>
@@ -5043,7 +5043,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>32.46213150024414</v>
+        <v>32.46212387084961</v>
       </c>
       <c r="C175" t="n">
         <v>38.65000152587891</v>
@@ -5101,7 +5101,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.32525444030762</v>
+        <v>31.32525825500488</v>
       </c>
       <c r="C177" t="n">
         <v>36.97999954223633</v>
@@ -5130,7 +5130,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>29.08894920349121</v>
+        <v>29.08895111083984</v>
       </c>
       <c r="C178" t="n">
         <v>34.34000015258789</v>
@@ -5159,7 +5159,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>29.35363960266113</v>
+        <v>29.3536319732666</v>
       </c>
       <c r="C179" t="n">
         <v>34.36000061035156</v>
@@ -5188,7 +5188,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>33.42008972167969</v>
+        <v>33.42007827758789</v>
       </c>
       <c r="C180" t="n">
         <v>39.11999893188477</v>
@@ -5275,7 +5275,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>36.29365539550781</v>
+        <v>36.29364776611328</v>
       </c>
       <c r="C183" t="n">
         <v>42.15999984741211</v>
@@ -5304,7 +5304,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>40.70984268188477</v>
+        <v>40.70984649658203</v>
       </c>
       <c r="C184" t="n">
         <v>47.29000091552734</v>
@@ -5333,7 +5333,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>43.21792984008789</v>
+        <v>43.21793746948242</v>
       </c>
       <c r="C185" t="n">
         <v>49.88000106811523</v>
@@ -5362,7 +5362,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>45.12410736083984</v>
+        <v>45.12409210205078</v>
       </c>
       <c r="C186" t="n">
         <v>52.08000183105469</v>
@@ -5391,7 +5391,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>44.38762283325195</v>
+        <v>44.38763046264648</v>
       </c>
       <c r="C187" t="n">
         <v>51.22999954223633</v>
@@ -5478,7 +5478,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>45.22385406494141</v>
+        <v>45.22386169433594</v>
       </c>
       <c r="C190" t="n">
         <v>51.84000015258789</v>
@@ -5507,7 +5507,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>51.94163513183594</v>
+        <v>51.94164276123047</v>
       </c>
       <c r="C191" t="n">
         <v>59.20000076293945</v>
@@ -5536,7 +5536,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>48.07235336303711</v>
+        <v>48.07234191894531</v>
       </c>
       <c r="C192" t="n">
         <v>54.79000091552734</v>
@@ -5594,7 +5594,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>52.29892349243164</v>
+        <v>52.29891967773438</v>
       </c>
       <c r="C194" t="n">
         <v>59.2599983215332</v>
@@ -5623,7 +5623,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>46.90664672851562</v>
+        <v>46.90663909912109</v>
       </c>
       <c r="C195" t="n">
         <v>53.15000152587891</v>
@@ -5652,7 +5652,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>43.80011749267578</v>
+        <v>43.80013656616211</v>
       </c>
       <c r="C196" t="n">
         <v>49.63000106811523</v>
@@ -5681,7 +5681,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>37.41340255737305</v>
+        <v>37.41339111328125</v>
       </c>
       <c r="C197" t="n">
         <v>42.06000137329102</v>
@@ -5739,7 +5739,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>37.10206985473633</v>
+        <v>37.10206604003906</v>
       </c>
       <c r="C199" t="n">
         <v>41.70999908447266</v>
@@ -5768,7 +5768,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>38.99052810668945</v>
+        <v>38.99053192138672</v>
       </c>
       <c r="C200" t="n">
         <v>43.45999908447266</v>
@@ -5797,7 +5797,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>37.25900650024414</v>
+        <v>37.25901031494141</v>
       </c>
       <c r="C201" t="n">
         <v>41.52999877929688</v>
@@ -5826,7 +5826,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>34.55855941772461</v>
+        <v>34.55856323242188</v>
       </c>
       <c r="C202" t="n">
         <v>38.52000045776367</v>
@@ -5884,7 +5884,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>41.54914855957031</v>
+        <v>41.54915237426758</v>
       </c>
       <c r="C204" t="n">
         <v>45.90000152587891</v>
@@ -5913,7 +5913,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>41.20516967773438</v>
+        <v>41.20516586303711</v>
       </c>
       <c r="C205" t="n">
         <v>45.52000045776367</v>
@@ -5942,7 +5942,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>46.12533187866211</v>
+        <v>46.12533950805664</v>
       </c>
       <c r="C206" t="n">
         <v>50.56999969482422</v>
@@ -5971,7 +5971,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.40808486938477</v>
+        <v>46.40808868408203</v>
       </c>
       <c r="C207" t="n">
         <v>50.88000106811523</v>
@@ -6029,7 +6029,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>39.1937255859375</v>
+        <v>39.19372177124023</v>
       </c>
       <c r="C209" t="n">
         <v>42.59000015258789</v>
@@ -6087,7 +6087,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>40.96981811523438</v>
+        <v>40.96982192993164</v>
       </c>
       <c r="C211" t="n">
         <v>44.52000045776367</v>
@@ -6116,7 +6116,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.13071441650391</v>
+        <v>42.13070678710938</v>
       </c>
       <c r="C212" t="n">
         <v>45.36000061035156</v>
@@ -6145,7 +6145,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>41.67559051513672</v>
+        <v>41.67559432983398</v>
       </c>
       <c r="C213" t="n">
         <v>44.86999893188477</v>
@@ -6174,7 +6174,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>39.61363983154297</v>
+        <v>39.61363220214844</v>
       </c>
       <c r="C214" t="n">
         <v>42.65000152587891</v>
@@ -6203,7 +6203,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>39.87449645996094</v>
+        <v>39.87449264526367</v>
       </c>
       <c r="C215" t="n">
         <v>42.5</v>
@@ -6232,7 +6232,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>45.3349609375</v>
+        <v>45.3349494934082</v>
       </c>
       <c r="C216" t="n">
         <v>48.31999969482422</v>
@@ -6261,7 +6261,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>48.83452606201172</v>
+        <v>48.83453369140625</v>
       </c>
       <c r="C217" t="n">
         <v>52.04999923706055</v>
@@ -6319,7 +6319,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>53.03260040283203</v>
+        <v>53.03259658813477</v>
       </c>
       <c r="C219" t="n">
         <v>56.09000015258789</v>
@@ -6348,7 +6348,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>54.47919082641602</v>
+        <v>54.47920227050781</v>
       </c>
       <c r="C220" t="n">
         <v>57.61999893188477</v>
@@ -6377,7 +6377,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>53.80071640014648</v>
+        <v>53.80072021484375</v>
       </c>
       <c r="C221" t="n">
         <v>56.4900016784668</v>
@@ -6406,7 +6406,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>56.77218246459961</v>
+        <v>56.77219009399414</v>
       </c>
       <c r="C222" t="n">
         <v>59.61000061035156</v>
@@ -6435,7 +6435,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>57.03884887695312</v>
+        <v>57.03885269165039</v>
       </c>
       <c r="C223" t="n">
         <v>59.88999938964844</v>
@@ -6464,7 +6464,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>62.44038391113281</v>
+        <v>62.44038772583008</v>
       </c>
       <c r="C224" t="n">
         <v>65.06999969482422</v>
@@ -6522,7 +6522,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>68.95597839355469</v>
+        <v>68.95597076416016</v>
       </c>
       <c r="C226" t="n">
         <v>71.86000061035156</v>
@@ -6551,7 +6551,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>72.76057434082031</v>
+        <v>72.76058197021484</v>
       </c>
       <c r="C227" t="n">
         <v>75.36000061035156</v>
@@ -6580,7 +6580,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>79.04602813720703</v>
+        <v>79.04603576660156</v>
       </c>
       <c r="C228" t="n">
         <v>81.87000274658203</v>
@@ -6609,7 +6609,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>74.17987060546875</v>
+        <v>74.17987823486328</v>
       </c>
       <c r="C229" t="n">
         <v>76.83000183105469</v>
@@ -6638,7 +6638,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>83.42301177978516</v>
+        <v>83.42302703857422</v>
       </c>
       <c r="C230" t="n">
         <v>85.93000030517578</v>
@@ -6667,7 +6667,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>86.35491180419922</v>
+        <v>86.35490417480469</v>
       </c>
       <c r="C231" t="n">
         <v>88.94999694824219</v>
@@ -6696,7 +6696,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>81.42310333251953</v>
+        <v>81.42311859130859</v>
       </c>
       <c r="C232" t="n">
         <v>83.87000274658203</v>
@@ -6725,7 +6725,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>78.54766082763672</v>
+        <v>78.54765319824219</v>
       </c>
       <c r="C233" t="n">
         <v>80.41000366210938</v>
@@ -6754,7 +6754,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>86.55773162841797</v>
+        <v>86.5577392578125</v>
       </c>
       <c r="C234" t="n">
         <v>88.61000061035156</v>
@@ -6783,7 +6783,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.99982452392578</v>
+        <v>88.99983978271484</v>
       </c>
       <c r="C235" t="n">
         <v>91.11000061035156</v>
@@ -6870,7 +6870,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>107.0037078857422</v>
+        <v>107.0037002563477</v>
       </c>
       <c r="C238" t="n">
         <v>108.9599990844727</v>
@@ -6986,7 +6986,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>118.9219818115234</v>
+        <v>118.9219741821289</v>
       </c>
       <c r="C242" t="n">
         <v>119.9199981689453</v>
